--- a/Short Semester I (E24 Batch).xlsx
+++ b/Short Semester I (E24 Batch).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoj-my.sharepoint.com/personal/mayooran_eng_jfn_ac_lk/Documents/Short_Semesters/app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_557BE1177AF289A6DECF20E4DF96C4CEA6937B2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{913B5168-A63D-453E-B10B-B6C5A542367C}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_557BE1177AF289A6DECF20E4DF96C4CEA6937B2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E356BC1-AE70-40F2-8A0F-884D4838FF27}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MC9030" sheetId="2" r:id="rId1"/>
@@ -2974,7 +2974,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2997,6 +2997,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14034,7 +14038,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="116" customWidth="1"/>
-    <col min="2" max="2" width="73.28515625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" style="12" customWidth="1"/>
     <col min="3" max="3" width="12" style="12" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" style="13" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" style="13" bestFit="1" customWidth="1"/>
@@ -18217,7 +18221,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
-    <col min="2" max="2" width="87.85546875" customWidth="1"/>
+    <col min="2" max="2" width="31.5703125" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="7" width="17.28515625" style="1" customWidth="1"/>
   </cols>
@@ -20892,26 +20896,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100455C4072EA7E0D46870C67AD0D3E62C3" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6d62d4992a7888825600c982e6c75641">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2835d969-06cc-46e6-b4cc-c525f784ce43" xmlns:ns3="03c84e3c-1549-479a-8619-e0d964aa7481" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9015832621b6abd41b87bce5adc31c29" ns2:_="" ns3:_="">
     <xsd:import namespace="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
@@ -21166,32 +21150,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46A244EB-A970-4F2B-8B12-6A24EFA3E1AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21208,4 +21187,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Short Semester I (E24 Batch).xlsx
+++ b/Short Semester I (E24 Batch).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoj-my.sharepoint.com/personal/mayooran_eng_jfn_ac_lk/Documents/Short_Semesters/app/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\theva\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_557BE1177AF289A6DECF20E4DF96C4CEA6937B2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6571BAD7-2D56-4A9F-8C51-108884F09960}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51ED7CA-EA5E-4948-9CC4-917249FF1C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MC9030" sheetId="2" r:id="rId1"/>
@@ -2165,7 +2165,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2297,6 +2297,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Palatino Linotype"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
     </font>
   </fonts>
@@ -2562,7 +2568,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2750,6 +2756,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2770,10 +2779,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13558,8 +13563,8 @@
       <c r="C111" s="7" t="s">
         <v>559</v>
       </c>
-      <c r="D111" s="10">
-        <v>0</v>
+      <c r="D111" s="69">
+        <v>70</v>
       </c>
       <c r="E111" s="11">
         <v>62.5</v>
@@ -20374,12 +20379,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20638,20 +20645,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -20676,18 +20690,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Short Semester I (E24 Batch).xlsx
+++ b/Short Semester I (E24 Batch).xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\theva\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maids.jfn\Documents\GitHub\MC3020_Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51ED7CA-EA5E-4948-9CC4-917249FF1C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="MC9030" sheetId="2" r:id="rId1"/>
@@ -2164,7 +2163,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2314,7 +2313,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -2559,6 +2558,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2568,7 +2578,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2759,14 +2769,17 @@
     <xf numFmtId="2" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 15" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal_Sheet1" xfId="1" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Normal_Sheet1_1" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal 15" xfId="2"/>
+    <cellStyle name="Normal 2" xfId="3"/>
+    <cellStyle name="Normal 2 2" xfId="4"/>
+    <cellStyle name="Normal_Sheet1" xfId="1"/>
+    <cellStyle name="Normal_Sheet1_1" xfId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3043,7 +3056,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G210"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7466,7 +7479,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G178"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11228,8 +11241,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G122"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G123"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
@@ -13805,13 +13818,16 @@
       </c>
       <c r="G122" s="68"/>
     </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="70"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G198"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -17916,7 +17932,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB6E2A7E-2D4B-4BFC-938E-45B79060EAA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G177"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20379,17 +20395,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100455C4072EA7E0D46870C67AD0D3E62C3" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6d62d4992a7888825600c982e6c75641">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2835d969-06cc-46e6-b4cc-c525f784ce43" xmlns:ns3="03c84e3c-1549-479a-8619-e0d964aa7481" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9015832621b6abd41b87bce5adc31c29" ns2:_="" ns3:_="">
     <xsd:import namespace="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
@@ -20644,7 +20649,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -20653,24 +20658,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46A244EB-A970-4F2B-8B12-6A24EFA3E1AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20689,10 +20688,27 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Short Semester I (E24 Batch).xlsx
+++ b/Short Semester I (E24 Batch).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="MC9030" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="687">
   <si>
     <t>No.</t>
   </si>
@@ -2079,85 +2079,22 @@
     <t xml:space="preserve"> BANDARA J.M.S.U</t>
   </si>
   <si>
-    <t>AMBAGASPITIYE GEDARA DINITHI VIHANGA</t>
-  </si>
-  <si>
-    <t>GOPAL ABILAJAN</t>
-  </si>
-  <si>
-    <t>KURUPPU MUDIYANSELAGE LAKMIKA IRUSHA KURUPPU</t>
-  </si>
-  <si>
-    <t>MARAKA MUDIYANSELAGE SANUDA SANHITHA BANDARA WIJERATHNA</t>
-  </si>
-  <si>
-    <t>MUZAMMIL MOHAMED INZAF</t>
-  </si>
-  <si>
-    <t>2024/E/094</t>
-  </si>
-  <si>
-    <t>SEMASINGHE NAWARATHNA WANNINAYAKE MUDIYANSELAGE KAVEESHA NETHMINI</t>
-  </si>
-  <si>
-    <t>SHERMAL KESHAWA WIDANA ARACHCHI</t>
-  </si>
-  <si>
-    <t>SIVABALAN RATHUSHAN</t>
-  </si>
-  <si>
-    <t>2024/E/128</t>
-  </si>
-  <si>
-    <t>WARAKAMURE GEDARA AYESHA MADHUMALI LANKA ARIYARATHNE</t>
-  </si>
-  <si>
-    <t>WARNAKULASOORIYA RASITHA JAYALATH LOWE</t>
-  </si>
-  <si>
-    <t>WARNAKULASURIYA INUSHI ASHINSHANA FERNANDO</t>
-  </si>
-  <si>
-    <t>WEDAGE ANUJA DHUSARA VIBHAVITH WIJAYANANDA</t>
-  </si>
-  <si>
-    <t>WEERATHUNGA MUDIYANSELAGE PRABHANEE CHETHANI</t>
-  </si>
-  <si>
-    <t>WIJEKOON MUDIYANSELAGE GIHAN SASSARA THENNAKOON</t>
-  </si>
-  <si>
-    <t>2024/E/171</t>
-  </si>
-  <si>
-    <t>YESIL BIMSARA DHARMADASA</t>
-  </si>
-  <si>
-    <t>2024/E/179</t>
-  </si>
-  <si>
-    <t>KUTHADIGE AYESH OSHARA FERNANDO</t>
-  </si>
-  <si>
-    <t>2024/E/191</t>
-  </si>
-  <si>
-    <t>RAJAWARDHANA GEDARA NIPUN MALEESHA RAJAWARDHANA</t>
-  </si>
-  <si>
-    <t>WEDAMESTHRIGE ROSHEN SHEHARA SILVA</t>
-  </si>
-  <si>
-    <t>GONNAGAHAPITIYE GEDARA PASINDU NIMSARA WIJESOORIYA</t>
-  </si>
-  <si>
     <t>2021/E/040</t>
   </si>
   <si>
-    <t>RATHNAYAKA MUDIYANSELAGE KAVINDU ISHARA RATHNAYAKA</t>
-  </si>
-  <si>
     <t>2021/E/132</t>
+  </si>
+  <si>
+    <t>SAMARANAYAKE S.R.MM.D.</t>
+  </si>
+  <si>
+    <t>DISSANAYAKA D.M.I.I.</t>
+  </si>
+  <si>
+    <t>WIJESOORIYA G.G.P.N.</t>
+  </si>
+  <si>
+    <t>RATHNAYAKA R.M.K.I.</t>
   </si>
 </sst>
 </file>
@@ -2305,12 +2242,18 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="19">
@@ -2578,7 +2521,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2771,6 +2714,30 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -17933,2460 +17900,3286 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G177"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+    <row r="1" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="71" t="s">
         <v>427</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="71" t="s">
         <v>428</v>
       </c>
-      <c r="F1" s="40" t="s">
+      <c r="F1" s="71" t="s">
         <v>429</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="G1" s="71" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43">
+      <c r="A2" s="72">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>591</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="44"/>
+      <c r="D2" s="78">
+        <v>0</v>
+      </c>
+      <c r="E2" s="11">
+        <v>49</v>
+      </c>
+      <c r="F2" s="77">
+        <v>0</v>
+      </c>
+      <c r="G2" s="73"/>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43">
+      <c r="A3" s="72">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>592</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="44"/>
+      <c r="D3" s="11">
+        <v>84</v>
+      </c>
+      <c r="E3" s="11">
+        <v>55</v>
+      </c>
+      <c r="F3" s="10">
+        <v>80</v>
+      </c>
+      <c r="G3" s="73"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="43">
+      <c r="A4" s="72">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>432</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="44"/>
+        <v>11</v>
+      </c>
+      <c r="D4" s="11">
+        <v>74</v>
+      </c>
+      <c r="E4" s="11">
+        <v>41</v>
+      </c>
+      <c r="F4" s="10">
+        <v>90</v>
+      </c>
+      <c r="G4" s="73"/>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="43">
+      <c r="A5" s="72">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>433</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="44"/>
+      <c r="D5" s="11">
+        <v>84</v>
+      </c>
+      <c r="E5" s="11">
+        <v>64</v>
+      </c>
+      <c r="F5" s="10">
+        <v>75</v>
+      </c>
+      <c r="G5" s="73"/>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="43">
+      <c r="A6" s="72">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>14</v>
+        <v>434</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="44"/>
+      <c r="D6" s="11">
+        <v>80</v>
+      </c>
+      <c r="E6" s="11">
+        <v>73</v>
+      </c>
+      <c r="F6" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="G6" s="73"/>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="43">
+      <c r="A7" s="72">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>435</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="44"/>
+      <c r="D7" s="11">
+        <v>78</v>
+      </c>
+      <c r="E7" s="11">
+        <v>85</v>
+      </c>
+      <c r="F7" s="10">
+        <v>90</v>
+      </c>
+      <c r="G7" s="73"/>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="43">
+      <c r="A8" s="72">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>681</v>
+        <v>436</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="44"/>
+      <c r="D8" s="11">
+        <v>74</v>
+      </c>
+      <c r="E8" s="11">
+        <v>67</v>
+      </c>
+      <c r="F8" s="10">
+        <v>90</v>
+      </c>
+      <c r="G8" s="73"/>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="43">
+      <c r="A9" s="72">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>19</v>
+        <v>593</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="44"/>
+      <c r="D9" s="11">
+        <v>84</v>
+      </c>
+      <c r="E9" s="11">
+        <v>80</v>
+      </c>
+      <c r="F9" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="G9" s="73"/>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="43">
+      <c r="A10" s="72">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>437</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="44"/>
+      <c r="D10" s="11">
+        <v>80</v>
+      </c>
+      <c r="E10" s="11">
+        <v>51</v>
+      </c>
+      <c r="F10" s="10">
+        <v>80</v>
+      </c>
+      <c r="G10" s="73"/>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="43">
+      <c r="A11" s="72">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>23</v>
+        <v>594</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="44"/>
+      <c r="D11" s="11">
+        <v>70</v>
+      </c>
+      <c r="E11" s="11">
+        <v>64</v>
+      </c>
+      <c r="F11" s="10">
+        <v>82.5</v>
+      </c>
+      <c r="G11" s="73"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="43">
+      <c r="A12" s="72">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>25</v>
+        <v>595</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="44"/>
+      <c r="D12" s="11">
+        <v>74</v>
+      </c>
+      <c r="E12" s="11">
+        <v>63</v>
+      </c>
+      <c r="F12" s="10">
+        <v>80</v>
+      </c>
+      <c r="G12" s="73"/>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43">
+      <c r="A13" s="72">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="11">
+        <v>74</v>
+      </c>
+      <c r="E13" s="11">
+        <v>78</v>
+      </c>
+      <c r="F13" s="10">
+        <v>80</v>
+      </c>
+      <c r="G13" s="73"/>
+    </row>
+    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="72">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="11">
+        <v>76</v>
+      </c>
+      <c r="E14" s="11">
+        <v>51</v>
+      </c>
+      <c r="F14" s="10">
+        <v>82.5</v>
+      </c>
+      <c r="G14" s="73"/>
+    </row>
+    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="72">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="11">
+        <v>60</v>
+      </c>
+      <c r="E15" s="11">
+        <v>39</v>
+      </c>
+      <c r="F15" s="10">
+        <v>70</v>
+      </c>
+      <c r="G15" s="73"/>
+    </row>
+    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="72">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="11">
+        <v>80</v>
+      </c>
+      <c r="E16" s="11">
+        <v>87</v>
+      </c>
+      <c r="F16" s="10">
+        <v>75</v>
+      </c>
+      <c r="G16" s="73"/>
+    </row>
+    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="72">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="11">
+        <v>84</v>
+      </c>
+      <c r="E17" s="11">
+        <v>70</v>
+      </c>
+      <c r="F17" s="10">
+        <v>85</v>
+      </c>
+      <c r="G17" s="73"/>
+    </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="72">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="11">
+        <v>72</v>
+      </c>
+      <c r="E18" s="11">
+        <v>73</v>
+      </c>
+      <c r="F18" s="10">
+        <v>90</v>
+      </c>
+      <c r="G18" s="73"/>
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="72">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="11">
+        <v>70</v>
+      </c>
+      <c r="E19" s="11">
+        <v>57</v>
+      </c>
+      <c r="F19" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="G19" s="73"/>
+    </row>
+    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="72">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="11">
+        <v>72</v>
+      </c>
+      <c r="E20" s="11">
+        <v>58</v>
+      </c>
+      <c r="F20" s="10">
+        <v>82.5</v>
+      </c>
+      <c r="G20" s="73"/>
+    </row>
+    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="72">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="11">
+        <v>76</v>
+      </c>
+      <c r="E21" s="11">
+        <v>66</v>
+      </c>
+      <c r="F21" s="10">
+        <v>82.5</v>
+      </c>
+      <c r="G21" s="73"/>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="72">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="11">
+        <v>72</v>
+      </c>
+      <c r="E22" s="11">
+        <v>64</v>
+      </c>
+      <c r="F22" s="10">
+        <v>80</v>
+      </c>
+      <c r="G22" s="73"/>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="72">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="11">
+        <v>84</v>
+      </c>
+      <c r="E23" s="11">
+        <v>63</v>
+      </c>
+      <c r="F23" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="G23" s="73"/>
+    </row>
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="72">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="11">
+        <v>80</v>
+      </c>
+      <c r="E24" s="11">
+        <v>59</v>
+      </c>
+      <c r="F24" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="G24" s="73"/>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="72">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="11">
+        <v>70</v>
+      </c>
+      <c r="E25" s="11">
+        <v>67</v>
+      </c>
+      <c r="F25" s="10">
+        <v>85</v>
+      </c>
+      <c r="G25" s="73"/>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="72">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="11">
+        <v>74</v>
+      </c>
+      <c r="E26" s="11">
+        <v>65</v>
+      </c>
+      <c r="F26" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="G26" s="73"/>
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="72">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="11">
+        <v>80</v>
+      </c>
+      <c r="E27" s="11">
+        <v>70</v>
+      </c>
+      <c r="F27" s="10">
+        <v>82.5</v>
+      </c>
+      <c r="G27" s="73"/>
+    </row>
+    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="72">
         <v>27</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="B28" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" s="11">
+        <v>74</v>
+      </c>
+      <c r="E28" s="11">
+        <v>72</v>
+      </c>
+      <c r="F28" s="10">
+        <v>90</v>
+      </c>
+      <c r="G28" s="73"/>
+    </row>
+    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="72">
         <v>28</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="44"/>
-    </row>
-    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="43">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="B29" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" s="11">
+        <v>70</v>
+      </c>
+      <c r="E29" s="11">
+        <v>47</v>
+      </c>
+      <c r="F29" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="G29" s="73"/>
+    </row>
+    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="72">
         <v>29</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="B30" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" s="11">
+        <v>70</v>
+      </c>
+      <c r="E30" s="11">
+        <v>44</v>
+      </c>
+      <c r="F30" s="10">
+        <v>82.5</v>
+      </c>
+      <c r="G30" s="73"/>
+    </row>
+    <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="72">
         <v>30</v>
       </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="44"/>
-    </row>
-    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="43">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="B31" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D31" s="11">
+        <v>70</v>
+      </c>
+      <c r="E31" s="11">
+        <v>48</v>
+      </c>
+      <c r="F31" s="10">
+        <v>75</v>
+      </c>
+      <c r="G31" s="73"/>
+    </row>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="72">
         <v>31</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="B32" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="11">
+        <v>84</v>
+      </c>
+      <c r="E32" s="11">
+        <v>44</v>
+      </c>
+      <c r="F32" s="10">
+        <v>82.5</v>
+      </c>
+      <c r="G32" s="73"/>
+    </row>
+    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="72">
         <v>32</v>
       </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="44"/>
-    </row>
-    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="43">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="B33" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D33" s="78">
+        <v>0</v>
+      </c>
+      <c r="E33" s="11">
+        <v>72</v>
+      </c>
+      <c r="F33" s="77">
+        <v>0</v>
+      </c>
+      <c r="G33" s="73"/>
+    </row>
+    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="72">
         <v>33</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="B34" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="11">
+        <v>70</v>
+      </c>
+      <c r="E34" s="11">
+        <v>52</v>
+      </c>
+      <c r="F34" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="G34" s="73"/>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="72">
         <v>34</v>
       </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="44"/>
-    </row>
-    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="43">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="B35" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" s="11">
+        <v>72</v>
+      </c>
+      <c r="E35" s="11">
+        <v>56</v>
+      </c>
+      <c r="F35" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="G35" s="73"/>
+    </row>
+    <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="72">
         <v>35</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="B36" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D36" s="11">
+        <v>80</v>
+      </c>
+      <c r="E36" s="11">
+        <v>70</v>
+      </c>
+      <c r="F36" s="10">
+        <v>82.5</v>
+      </c>
+      <c r="G36" s="73"/>
+    </row>
+    <row r="37" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="72">
         <v>36</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="44"/>
-    </row>
-    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="43">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="B37" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D37" s="11">
+        <v>70</v>
+      </c>
+      <c r="E37" s="11">
+        <v>76</v>
+      </c>
+      <c r="F37" s="10">
+        <v>92.5</v>
+      </c>
+      <c r="G37" s="73"/>
+    </row>
+    <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="72">
         <v>37</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="B38" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D38" s="11">
+        <v>84</v>
+      </c>
+      <c r="E38" s="11">
+        <v>54</v>
+      </c>
+      <c r="F38" s="10">
+        <v>92.5</v>
+      </c>
+      <c r="G38" s="73"/>
+    </row>
+    <row r="39" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="72">
         <v>38</v>
       </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="44"/>
-    </row>
-    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="43">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
+      <c r="B39" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D39" s="11">
+        <v>80</v>
+      </c>
+      <c r="E39" s="11">
+        <v>74</v>
+      </c>
+      <c r="F39" s="10">
+        <v>90</v>
+      </c>
+      <c r="G39" s="73"/>
+    </row>
+    <row r="40" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="72">
         <v>39</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="B40" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D40" s="11">
+        <v>76</v>
+      </c>
+      <c r="E40" s="11">
+        <v>66</v>
+      </c>
+      <c r="F40" s="10">
+        <v>95</v>
+      </c>
+      <c r="G40" s="73"/>
+    </row>
+    <row r="41" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="72">
         <v>40</v>
       </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="44"/>
-    </row>
-    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="43">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="B41" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D41" s="11">
+        <v>70</v>
+      </c>
+      <c r="E41" s="11">
+        <v>40</v>
+      </c>
+      <c r="F41" s="10">
+        <v>75</v>
+      </c>
+      <c r="G41" s="73"/>
+    </row>
+    <row r="42" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="72">
         <v>41</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="B42" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42" s="11">
+        <v>72</v>
+      </c>
+      <c r="E42" s="11">
+        <v>63</v>
+      </c>
+      <c r="F42" s="10">
+        <v>80</v>
+      </c>
+      <c r="G42" s="73"/>
+    </row>
+    <row r="43" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="72">
         <v>42</v>
       </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="44"/>
-    </row>
-    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="43">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="B43" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D43" s="11">
+        <v>74</v>
+      </c>
+      <c r="E43" s="11">
+        <v>61</v>
+      </c>
+      <c r="F43" s="10">
+        <v>82.5</v>
+      </c>
+      <c r="G43" s="73"/>
+    </row>
+    <row r="44" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="72">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D44" s="11">
+        <v>80</v>
+      </c>
+      <c r="E44" s="11">
+        <v>80</v>
+      </c>
+      <c r="F44" s="10">
+        <v>85</v>
+      </c>
+      <c r="G44" s="73"/>
+    </row>
+    <row r="45" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="72">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D45" s="11">
+        <v>80</v>
+      </c>
+      <c r="E45" s="11">
+        <v>82</v>
+      </c>
+      <c r="F45" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="G45" s="73"/>
+    </row>
+    <row r="46" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="72">
         <v>45</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="B46" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D46" s="11">
+        <v>80</v>
+      </c>
+      <c r="E46" s="11">
+        <v>55</v>
+      </c>
+      <c r="F46" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="G46" s="73"/>
+    </row>
+    <row r="47" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="72">
         <v>46</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="44"/>
-    </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="43">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="B47" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D47" s="11">
+        <v>70</v>
+      </c>
+      <c r="E47" s="11">
+        <v>76</v>
+      </c>
+      <c r="F47" s="10">
+        <v>80</v>
+      </c>
+      <c r="G47" s="73"/>
+    </row>
+    <row r="48" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="72">
         <v>47</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="B48" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D48" s="11">
+        <v>80</v>
+      </c>
+      <c r="E48" s="11">
+        <v>52</v>
+      </c>
+      <c r="F48" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="G48" s="73"/>
+    </row>
+    <row r="49" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="72">
         <v>48</v>
       </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="44"/>
-    </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="43">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="B49" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D49" s="11">
+        <v>72</v>
+      </c>
+      <c r="E49" s="11">
+        <v>61</v>
+      </c>
+      <c r="F49" s="10">
+        <v>82.5</v>
+      </c>
+      <c r="G49" s="73"/>
+    </row>
+    <row r="50" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="72">
         <v>49</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="B50" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D50" s="11">
+        <v>78</v>
+      </c>
+      <c r="E50" s="11">
+        <v>69</v>
+      </c>
+      <c r="F50" s="10">
+        <v>80</v>
+      </c>
+      <c r="G50" s="73"/>
+    </row>
+    <row r="51" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="72">
         <v>50</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="44"/>
-    </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="43">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
+      <c r="B51" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D51" s="11">
+        <v>80</v>
+      </c>
+      <c r="E51" s="11">
+        <v>63</v>
+      </c>
+      <c r="F51" s="10">
+        <v>80</v>
+      </c>
+      <c r="G51" s="73"/>
+    </row>
+    <row r="52" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="72">
         <v>51</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="B52" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D52" s="11">
+        <v>76</v>
+      </c>
+      <c r="E52" s="11">
+        <v>45</v>
+      </c>
+      <c r="F52" s="10">
+        <v>82.5</v>
+      </c>
+      <c r="G52" s="73"/>
+    </row>
+    <row r="53" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="72">
         <v>52</v>
       </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="44"/>
-    </row>
-    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="43">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="B53" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D53" s="11">
+        <v>70</v>
+      </c>
+      <c r="E53" s="11">
+        <v>61</v>
+      </c>
+      <c r="F53" s="10">
+        <v>70</v>
+      </c>
+      <c r="G53" s="73"/>
+    </row>
+    <row r="54" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="72">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D54" s="11">
+        <v>70</v>
+      </c>
+      <c r="E54" s="11">
+        <v>65</v>
+      </c>
+      <c r="F54" s="10">
+        <v>60</v>
+      </c>
+      <c r="G54" s="73"/>
+    </row>
+    <row r="55" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="72">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D55" s="11">
+        <v>80</v>
+      </c>
+      <c r="E55" s="11">
+        <v>75</v>
+      </c>
+      <c r="F55" s="10">
+        <v>70</v>
+      </c>
+      <c r="G55" s="73"/>
+    </row>
+    <row r="56" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="72">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D56" s="11">
+        <v>70</v>
+      </c>
+      <c r="E56" s="11">
+        <v>33</v>
+      </c>
+      <c r="F56" s="10">
+        <v>50</v>
+      </c>
+      <c r="G56" s="73"/>
+    </row>
+    <row r="57" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="72">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D57" s="11">
+        <v>70</v>
+      </c>
+      <c r="E57" s="11">
+        <v>53</v>
+      </c>
+      <c r="F57" s="10">
+        <v>60</v>
+      </c>
+      <c r="G57" s="73"/>
+    </row>
+    <row r="58" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="72">
         <v>57</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="B58" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D58" s="11">
+        <v>70</v>
+      </c>
+      <c r="E58" s="11">
+        <v>41</v>
+      </c>
+      <c r="F58" s="10">
+        <v>80</v>
+      </c>
+      <c r="G58" s="73"/>
+    </row>
+    <row r="59" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="72">
         <v>58</v>
       </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="44"/>
-    </row>
-    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="43">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
+      <c r="B59" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D59" s="11">
+        <v>70</v>
+      </c>
+      <c r="E59" s="11">
+        <v>54</v>
+      </c>
+      <c r="F59" s="10">
+        <v>60</v>
+      </c>
+      <c r="G59" s="73"/>
+    </row>
+    <row r="60" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="72">
         <v>59</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="B60" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D60" s="11">
+        <v>70</v>
+      </c>
+      <c r="E60" s="11">
+        <v>66</v>
+      </c>
+      <c r="F60" s="10">
         <v>60</v>
       </c>
-      <c r="D26" s="10"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="44"/>
-    </row>
-    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="43">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="s">
+      <c r="G60" s="73"/>
+    </row>
+    <row r="61" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="72">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D61" s="11">
+        <v>70</v>
+      </c>
+      <c r="E61" s="11">
+        <v>37</v>
+      </c>
+      <c r="F61" s="10">
+        <v>50</v>
+      </c>
+      <c r="G61" s="73"/>
+    </row>
+    <row r="62" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="72">
         <v>61</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="B62" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D62" s="11">
+        <v>80</v>
+      </c>
+      <c r="E62" s="11">
+        <v>64</v>
+      </c>
+      <c r="F62" s="10">
+        <v>60</v>
+      </c>
+      <c r="G62" s="73"/>
+    </row>
+    <row r="63" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="72">
         <v>62</v>
       </c>
-      <c r="D27" s="10"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="44"/>
-    </row>
-    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="43">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="s">
+      <c r="B63" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D63" s="11">
+        <v>70</v>
+      </c>
+      <c r="E63" s="11">
+        <v>64</v>
+      </c>
+      <c r="F63" s="10">
+        <v>70</v>
+      </c>
+      <c r="G63" s="73"/>
+    </row>
+    <row r="64" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="72">
         <v>63</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="B64" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D64" s="11">
+        <v>80</v>
+      </c>
+      <c r="E64" s="11">
+        <v>72</v>
+      </c>
+      <c r="F64" s="10">
+        <v>60</v>
+      </c>
+      <c r="G64" s="73"/>
+    </row>
+    <row r="65" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="72">
         <v>64</v>
       </c>
-      <c r="D28" s="10"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="44"/>
-    </row>
-    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="43">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="s">
+      <c r="B65" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D65" s="11">
+        <v>80</v>
+      </c>
+      <c r="E65" s="11">
+        <v>78</v>
+      </c>
+      <c r="F65" s="10">
+        <v>60</v>
+      </c>
+      <c r="G65" s="73"/>
+    </row>
+    <row r="66" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="72">
         <v>65</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="B66" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D66" s="11">
+        <v>70</v>
+      </c>
+      <c r="E66" s="11">
+        <v>57</v>
+      </c>
+      <c r="F66" s="10">
+        <v>50</v>
+      </c>
+      <c r="G66" s="73"/>
+    </row>
+    <row r="67" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="72">
         <v>66</v>
       </c>
-      <c r="D29" s="10"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="44"/>
-    </row>
-    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="43">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="s">
+      <c r="B67" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D67" s="11">
+        <v>70</v>
+      </c>
+      <c r="E67" s="11">
+        <v>59</v>
+      </c>
+      <c r="F67" s="10">
+        <v>50</v>
+      </c>
+      <c r="G67" s="73"/>
+    </row>
+    <row r="68" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="72">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D68" s="11">
+        <v>70</v>
+      </c>
+      <c r="E68" s="11">
+        <v>41</v>
+      </c>
+      <c r="F68" s="10">
+        <v>80</v>
+      </c>
+      <c r="G68" s="73"/>
+    </row>
+    <row r="69" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="72">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D69" s="11">
+        <v>70</v>
+      </c>
+      <c r="E69" s="11">
+        <v>34</v>
+      </c>
+      <c r="F69" s="10">
+        <v>80</v>
+      </c>
+      <c r="G69" s="73"/>
+    </row>
+    <row r="70" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="72">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D70" s="11">
+        <v>70</v>
+      </c>
+      <c r="E70" s="11">
+        <v>42</v>
+      </c>
+      <c r="F70" s="10">
+        <v>50</v>
+      </c>
+      <c r="G70" s="73"/>
+    </row>
+    <row r="71" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="72">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D71" s="11">
+        <v>70</v>
+      </c>
+      <c r="E71" s="11">
+        <v>32</v>
+      </c>
+      <c r="F71" s="10">
+        <v>70</v>
+      </c>
+      <c r="G71" s="73"/>
+    </row>
+    <row r="72" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="72">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D72" s="11">
+        <v>70</v>
+      </c>
+      <c r="E72" s="11">
+        <v>64</v>
+      </c>
+      <c r="F72" s="10">
+        <v>70</v>
+      </c>
+      <c r="G72" s="73"/>
+    </row>
+    <row r="73" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="72">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D73" s="11">
+        <v>70</v>
+      </c>
+      <c r="E73" s="11">
+        <v>34</v>
+      </c>
+      <c r="F73" s="10">
+        <v>50</v>
+      </c>
+      <c r="G73" s="73"/>
+    </row>
+    <row r="74" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="72">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="D74" s="11">
+        <v>70</v>
+      </c>
+      <c r="E74" s="11">
+        <v>47</v>
+      </c>
+      <c r="F74" s="10">
+        <v>50</v>
+      </c>
+      <c r="G74" s="73"/>
+    </row>
+    <row r="75" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="72">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D75" s="11">
+        <v>70</v>
+      </c>
+      <c r="E75" s="11">
+        <v>40</v>
+      </c>
+      <c r="F75" s="10">
+        <v>60</v>
+      </c>
+      <c r="G75" s="73"/>
+    </row>
+    <row r="76" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="72">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="D76" s="11">
+        <v>70</v>
+      </c>
+      <c r="E76" s="11">
+        <v>82</v>
+      </c>
+      <c r="F76" s="10">
+        <v>50</v>
+      </c>
+      <c r="G76" s="73"/>
+    </row>
+    <row r="77" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="72">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D77" s="11">
+        <v>70</v>
+      </c>
+      <c r="E77" s="11">
+        <v>65</v>
+      </c>
+      <c r="F77" s="10">
+        <v>60</v>
+      </c>
+      <c r="G77" s="73"/>
+    </row>
+    <row r="78" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="72">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D78" s="11">
+        <v>70</v>
+      </c>
+      <c r="E78" s="11">
+        <v>63</v>
+      </c>
+      <c r="F78" s="10">
+        <v>70</v>
+      </c>
+      <c r="G78" s="73"/>
+    </row>
+    <row r="79" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="72">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D79" s="11">
+        <v>80</v>
+      </c>
+      <c r="E79" s="11">
+        <v>80</v>
+      </c>
+      <c r="F79" s="10">
+        <v>70</v>
+      </c>
+      <c r="G79" s="73"/>
+    </row>
+    <row r="80" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="72">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D80" s="11">
+        <v>80</v>
+      </c>
+      <c r="E80" s="11">
+        <v>58</v>
+      </c>
+      <c r="F80" s="10">
+        <v>60</v>
+      </c>
+      <c r="G80" s="73"/>
+    </row>
+    <row r="81" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="72">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D81" s="11">
+        <v>70</v>
+      </c>
+      <c r="E81" s="11">
+        <v>50</v>
+      </c>
+      <c r="F81" s="10">
+        <v>60</v>
+      </c>
+      <c r="G81" s="73"/>
+    </row>
+    <row r="82" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="72">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D82" s="11">
+        <v>80</v>
+      </c>
+      <c r="E82" s="11">
+        <v>80</v>
+      </c>
+      <c r="F82" s="10">
+        <v>70</v>
+      </c>
+      <c r="G82" s="73"/>
+    </row>
+    <row r="83" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="72">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D83" s="11">
+        <v>80</v>
+      </c>
+      <c r="E83" s="11">
+        <v>65</v>
+      </c>
+      <c r="F83" s="10">
+        <v>70</v>
+      </c>
+      <c r="G83" s="73"/>
+    </row>
+    <row r="84" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="72">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D84" s="11">
+        <v>70</v>
+      </c>
+      <c r="E84" s="11">
+        <v>58</v>
+      </c>
+      <c r="F84" s="10">
+        <v>70</v>
+      </c>
+      <c r="G84" s="73"/>
+    </row>
+    <row r="85" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="72">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D85" s="11">
+        <v>70</v>
+      </c>
+      <c r="E85" s="11">
+        <v>48</v>
+      </c>
+      <c r="F85" s="10">
+        <v>70</v>
+      </c>
+      <c r="G85" s="73"/>
+    </row>
+    <row r="86" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="72">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D86" s="11">
+        <v>70</v>
+      </c>
+      <c r="E86" s="11">
+        <v>63</v>
+      </c>
+      <c r="F86" s="10">
+        <v>60</v>
+      </c>
+      <c r="G86" s="73"/>
+    </row>
+    <row r="87" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="72">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D87" s="11">
+        <v>80</v>
+      </c>
+      <c r="E87" s="11">
+        <v>64</v>
+      </c>
+      <c r="F87" s="10">
+        <v>60</v>
+      </c>
+      <c r="G87" s="73"/>
+    </row>
+    <row r="88" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="72">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D88" s="11">
+        <v>70</v>
+      </c>
+      <c r="E88" s="11">
+        <v>63</v>
+      </c>
+      <c r="F88" s="10">
+        <v>60</v>
+      </c>
+      <c r="G88" s="73"/>
+    </row>
+    <row r="89" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A89" s="72">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D89" s="11">
+        <v>80</v>
+      </c>
+      <c r="E89" s="11">
+        <v>68</v>
+      </c>
+      <c r="F89" s="10">
+        <v>70</v>
+      </c>
+      <c r="G89" s="73"/>
+    </row>
+    <row r="90" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="72">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="D90" s="11">
+        <v>70</v>
+      </c>
+      <c r="E90" s="11">
+        <v>80</v>
+      </c>
+      <c r="F90" s="10">
+        <v>60</v>
+      </c>
+      <c r="G90" s="73"/>
+    </row>
+    <row r="91" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="72">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D91" s="11">
+        <v>70</v>
+      </c>
+      <c r="E91" s="11">
+        <v>72</v>
+      </c>
+      <c r="F91" s="10">
+        <v>70</v>
+      </c>
+      <c r="G91" s="73"/>
+    </row>
+    <row r="92" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="72">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D92" s="11">
+        <v>80</v>
+      </c>
+      <c r="E92" s="11">
+        <v>67</v>
+      </c>
+      <c r="F92" s="10">
+        <v>50</v>
+      </c>
+      <c r="G92" s="73"/>
+    </row>
+    <row r="93" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="72">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D93" s="11">
+        <v>70</v>
+      </c>
+      <c r="E93" s="11">
+        <v>65</v>
+      </c>
+      <c r="F93" s="10">
+        <v>60</v>
+      </c>
+      <c r="G93" s="73"/>
+    </row>
+    <row r="94" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="72">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="D94" s="11">
+        <v>80</v>
+      </c>
+      <c r="E94" s="11">
+        <v>78</v>
+      </c>
+      <c r="F94" s="10">
+        <v>70</v>
+      </c>
+      <c r="G94" s="73"/>
+    </row>
+    <row r="95" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="72">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="D95" s="11">
+        <v>70</v>
+      </c>
+      <c r="E95" s="11">
+        <v>70</v>
+      </c>
+      <c r="F95" s="10">
+        <v>70</v>
+      </c>
+      <c r="G95" s="73"/>
+    </row>
+    <row r="96" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="72">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="D96" s="11">
+        <v>70</v>
+      </c>
+      <c r="E96" s="11">
+        <v>66</v>
+      </c>
+      <c r="F96" s="10">
+        <v>70</v>
+      </c>
+      <c r="G96" s="73"/>
+    </row>
+    <row r="97" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="72">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="D97" s="11">
+        <v>70</v>
+      </c>
+      <c r="E97" s="11">
+        <v>75</v>
+      </c>
+      <c r="F97" s="10">
+        <v>80</v>
+      </c>
+      <c r="G97" s="73"/>
+    </row>
+    <row r="98" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="72">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="D98" s="11">
+        <v>70</v>
+      </c>
+      <c r="E98" s="11">
+        <v>70</v>
+      </c>
+      <c r="F98" s="10">
+        <v>70</v>
+      </c>
+      <c r="G98" s="73"/>
+    </row>
+    <row r="99" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="72">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D99" s="11">
+        <v>80</v>
+      </c>
+      <c r="E99" s="11">
+        <v>68</v>
+      </c>
+      <c r="F99" s="10">
+        <v>50</v>
+      </c>
+      <c r="G99" s="73"/>
+    </row>
+    <row r="100" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="72">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="D100" s="11">
+        <v>70</v>
+      </c>
+      <c r="E100" s="11">
+        <v>68</v>
+      </c>
+      <c r="F100" s="10">
+        <v>50</v>
+      </c>
+      <c r="G100" s="73"/>
+    </row>
+    <row r="101" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="72">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="D101" s="11">
+        <v>80</v>
+      </c>
+      <c r="E101" s="11">
+        <v>75</v>
+      </c>
+      <c r="F101" s="10">
+        <v>50</v>
+      </c>
+      <c r="G101" s="73"/>
+    </row>
+    <row r="102" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="72">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D102" s="11">
+        <v>80</v>
+      </c>
+      <c r="E102" s="11">
+        <v>79</v>
+      </c>
+      <c r="F102" s="10">
+        <v>50</v>
+      </c>
+      <c r="G102" s="73"/>
+    </row>
+    <row r="103" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="72">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D103" s="11">
+        <v>70</v>
+      </c>
+      <c r="E103" s="11">
+        <v>61</v>
+      </c>
+      <c r="F103" s="10">
+        <v>0</v>
+      </c>
+      <c r="G103" s="73"/>
+    </row>
+    <row r="104" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="72">
+        <v>103</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D104" s="11">
+        <v>70</v>
+      </c>
+      <c r="E104" s="11">
+        <v>80</v>
+      </c>
+      <c r="F104" s="10">
+        <v>50</v>
+      </c>
+      <c r="G104" s="73"/>
+    </row>
+    <row r="105" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="72">
+        <v>104</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D105" s="11">
+        <v>80</v>
+      </c>
+      <c r="E105" s="11">
+        <v>74</v>
+      </c>
+      <c r="F105" s="10">
+        <v>70</v>
+      </c>
+      <c r="G105" s="73"/>
+    </row>
+    <row r="106" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="72">
+        <v>105</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="D106" s="11">
+        <v>70</v>
+      </c>
+      <c r="E106" s="11">
+        <v>78</v>
+      </c>
+      <c r="F106" s="10">
+        <v>70</v>
+      </c>
+      <c r="G106" s="73"/>
+    </row>
+    <row r="107" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="72">
+        <v>106</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="D107" s="11">
+        <v>80</v>
+      </c>
+      <c r="E107" s="11">
+        <v>75</v>
+      </c>
+      <c r="F107" s="10">
+        <v>80</v>
+      </c>
+      <c r="G107" s="73"/>
+    </row>
+    <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A108" s="72">
+        <v>107</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D108" s="11">
+        <v>80</v>
+      </c>
+      <c r="E108" s="11">
+        <v>67</v>
+      </c>
+      <c r="F108" s="10">
+        <v>70</v>
+      </c>
+      <c r="G108" s="73"/>
+    </row>
+    <row r="109" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="72">
+        <v>108</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D109" s="11">
+        <v>80</v>
+      </c>
+      <c r="E109" s="11">
+        <v>54</v>
+      </c>
+      <c r="F109" s="10">
+        <v>80</v>
+      </c>
+      <c r="G109" s="73"/>
+    </row>
+    <row r="110" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="72">
+        <v>109</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="D110" s="11">
+        <v>80</v>
+      </c>
+      <c r="E110" s="11">
+        <v>74</v>
+      </c>
+      <c r="F110" s="10">
+        <v>90</v>
+      </c>
+      <c r="G110" s="73"/>
+    </row>
+    <row r="111" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="72">
+        <v>110</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D111" s="11">
+        <v>70</v>
+      </c>
+      <c r="E111" s="11">
+        <v>72</v>
+      </c>
+      <c r="F111" s="10">
+        <v>80</v>
+      </c>
+      <c r="G111" s="73"/>
+    </row>
+    <row r="112" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="72">
+        <v>111</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="D112" s="11">
+        <v>70</v>
+      </c>
+      <c r="E112" s="11">
+        <v>74</v>
+      </c>
+      <c r="F112" s="10">
+        <v>70</v>
+      </c>
+      <c r="G112" s="73"/>
+    </row>
+    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="72">
+        <v>112</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="D113" s="11">
+        <v>90</v>
+      </c>
+      <c r="E113" s="11">
+        <v>78</v>
+      </c>
+      <c r="F113" s="10">
+        <v>70</v>
+      </c>
+      <c r="G113" s="73"/>
+    </row>
+    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="72">
+        <v>113</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="D114" s="11">
+        <v>90</v>
+      </c>
+      <c r="E114" s="11">
+        <v>68</v>
+      </c>
+      <c r="F114" s="10">
+        <v>70</v>
+      </c>
+      <c r="G114" s="73"/>
+    </row>
+    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="72">
+        <v>114</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D115" s="11">
+        <v>80</v>
+      </c>
+      <c r="E115" s="11">
+        <v>57</v>
+      </c>
+      <c r="F115" s="10">
+        <v>80</v>
+      </c>
+      <c r="G115" s="73"/>
+    </row>
+    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="72">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D116" s="11">
+        <v>80</v>
+      </c>
+      <c r="E116" s="11">
+        <v>60</v>
+      </c>
+      <c r="F116" s="10">
+        <v>70</v>
+      </c>
+      <c r="G116" s="73"/>
+    </row>
+    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="72">
+        <v>116</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="D117" s="11">
+        <v>80</v>
+      </c>
+      <c r="E117" s="11">
+        <v>82</v>
+      </c>
+      <c r="F117" s="10">
+        <v>80</v>
+      </c>
+      <c r="G117" s="73"/>
+    </row>
+    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="72">
+        <v>117</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="D118" s="11">
+        <v>70</v>
+      </c>
+      <c r="E118" s="11">
+        <v>80</v>
+      </c>
+      <c r="F118" s="10">
+        <v>80</v>
+      </c>
+      <c r="G118" s="73"/>
+    </row>
+    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="72">
+        <v>118</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D119" s="11">
+        <v>70</v>
+      </c>
+      <c r="E119" s="11">
+        <v>76</v>
+      </c>
+      <c r="F119" s="10">
+        <v>80</v>
+      </c>
+      <c r="G119" s="73"/>
+    </row>
+    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="72">
+        <v>119</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="C120" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="D120" s="11">
+        <v>80</v>
+      </c>
+      <c r="E120" s="11">
+        <v>76</v>
+      </c>
+      <c r="F120" s="10">
+        <v>80</v>
+      </c>
+      <c r="G120" s="73"/>
+    </row>
+    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="72">
+        <v>120</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D121" s="11">
+        <v>80</v>
+      </c>
+      <c r="E121" s="11">
+        <v>72</v>
+      </c>
+      <c r="F121" s="10">
+        <v>70</v>
+      </c>
+      <c r="G121" s="73"/>
+    </row>
+    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="72">
+        <v>121</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="C122" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="D122" s="11">
+        <v>70</v>
+      </c>
+      <c r="E122" s="11">
+        <v>58</v>
+      </c>
+      <c r="F122" s="10">
+        <v>70</v>
+      </c>
+      <c r="G122" s="73"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="72">
+        <v>122</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="D123" s="11">
+        <v>80</v>
+      </c>
+      <c r="E123" s="11">
+        <v>68</v>
+      </c>
+      <c r="F123" s="10">
+        <v>80</v>
+      </c>
+      <c r="G123" s="72"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="72">
+        <v>123</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="C124" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="D124" s="11">
+        <v>70</v>
+      </c>
+      <c r="E124" s="11">
+        <v>63</v>
+      </c>
+      <c r="F124" s="10">
+        <v>70</v>
+      </c>
+      <c r="G124" s="72"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="72">
+        <v>124</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="D125" s="11">
+        <v>70</v>
+      </c>
+      <c r="E125" s="11">
+        <v>80</v>
+      </c>
+      <c r="F125" s="10">
+        <v>80</v>
+      </c>
+      <c r="G125" s="72"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="72">
+        <v>125</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="C126" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="D126" s="11">
+        <v>80</v>
+      </c>
+      <c r="E126" s="11">
+        <v>65</v>
+      </c>
+      <c r="F126" s="10">
+        <v>70</v>
+      </c>
+      <c r="G126" s="72"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="72">
+        <v>126</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="C127" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="D127" s="11">
+        <v>70</v>
+      </c>
+      <c r="E127" s="11">
+        <v>66</v>
+      </c>
+      <c r="F127" s="10">
+        <v>70</v>
+      </c>
+      <c r="G127" s="72"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="72">
+        <v>127</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="C128" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="D128" s="11">
+        <v>80</v>
+      </c>
+      <c r="E128" s="11">
+        <v>80</v>
+      </c>
+      <c r="F128" s="10">
+        <v>70</v>
+      </c>
+      <c r="G128" s="72"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="72">
+        <v>128</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="C129" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D129" s="11">
+        <v>80</v>
+      </c>
+      <c r="E129" s="11">
+        <v>68</v>
+      </c>
+      <c r="F129" s="10">
+        <v>70</v>
+      </c>
+      <c r="G129" s="72"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="72">
+        <v>129</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="C130" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="D130" s="11">
+        <v>70</v>
+      </c>
+      <c r="E130" s="11">
+        <v>78</v>
+      </c>
+      <c r="F130" s="10">
+        <v>80</v>
+      </c>
+      <c r="G130" s="72"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="72">
+        <v>130</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="C131" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="D131" s="11">
+        <v>70</v>
+      </c>
+      <c r="E131" s="11">
+        <v>80</v>
+      </c>
+      <c r="F131" s="10">
+        <v>80</v>
+      </c>
+      <c r="G131" s="72"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" s="72">
+        <v>131</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="C132" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="D132" s="11">
+        <v>80</v>
+      </c>
+      <c r="E132" s="11">
+        <v>70</v>
+      </c>
+      <c r="F132" s="77"/>
+      <c r="G132" s="72"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" s="72">
+        <v>132</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="C133" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="D133" s="11">
+        <v>80</v>
+      </c>
+      <c r="E133" s="11">
+        <v>75</v>
+      </c>
+      <c r="F133" s="10">
+        <v>70</v>
+      </c>
+      <c r="G133" s="72"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" s="72">
+        <v>133</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>664</v>
+      </c>
+      <c r="C134" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="D134" s="11">
+        <v>80</v>
+      </c>
+      <c r="E134" s="11">
+        <v>54</v>
+      </c>
+      <c r="F134" s="10">
+        <v>70</v>
+      </c>
+      <c r="G134" s="72"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" s="72">
+        <v>134</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="C135" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="D135" s="11">
+        <v>70</v>
+      </c>
+      <c r="E135" s="11">
+        <v>64</v>
+      </c>
+      <c r="F135" s="10">
+        <v>80</v>
+      </c>
+      <c r="G135" s="72"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" s="72">
+        <v>135</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="C136" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="D136" s="11">
+        <v>80</v>
+      </c>
+      <c r="E136" s="11">
+        <v>80</v>
+      </c>
+      <c r="F136" s="10">
+        <v>70</v>
+      </c>
+      <c r="G136" s="72"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="72">
+        <v>136</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="C137" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="D137" s="11">
+        <v>80</v>
+      </c>
+      <c r="E137" s="11">
+        <v>60</v>
+      </c>
+      <c r="F137" s="10">
+        <v>90</v>
+      </c>
+      <c r="G137" s="72"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="72">
+        <v>137</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="C138" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="D138" s="11">
+        <v>70</v>
+      </c>
+      <c r="E138" s="11">
+        <v>60</v>
+      </c>
+      <c r="F138" s="10">
+        <v>70</v>
+      </c>
+      <c r="G138" s="72"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="72">
+        <v>138</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="C139" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="D139" s="11">
+        <v>70</v>
+      </c>
+      <c r="E139" s="11">
+        <v>70</v>
+      </c>
+      <c r="F139" s="10">
+        <v>70</v>
+      </c>
+      <c r="G139" s="72"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" s="72">
+        <v>139</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="C140" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="D140" s="11">
+        <v>70</v>
+      </c>
+      <c r="E140" s="11">
+        <v>68</v>
+      </c>
+      <c r="F140" s="10">
+        <v>80</v>
+      </c>
+      <c r="G140" s="72"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" s="72">
+        <v>140</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="C141" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="D141" s="11">
+        <v>90</v>
+      </c>
+      <c r="E141" s="11">
+        <v>64</v>
+      </c>
+      <c r="F141" s="10">
+        <v>80</v>
+      </c>
+      <c r="G141" s="72"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" s="72">
+        <v>141</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="C142" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="D142" s="11">
+        <v>80</v>
+      </c>
+      <c r="E142" s="11">
+        <v>58</v>
+      </c>
+      <c r="F142" s="10">
+        <v>80</v>
+      </c>
+      <c r="G142" s="72"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="72">
+        <v>142</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="C143" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="D143" s="11">
+        <v>70</v>
+      </c>
+      <c r="E143" s="11">
+        <v>72</v>
+      </c>
+      <c r="F143" s="10">
+        <v>80</v>
+      </c>
+      <c r="G143" s="72"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="72">
+        <v>143</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="C144" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="D144" s="11">
+        <v>80</v>
+      </c>
+      <c r="E144" s="11">
+        <v>68</v>
+      </c>
+      <c r="F144" s="10">
+        <v>70</v>
+      </c>
+      <c r="G144" s="72"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="72">
+        <v>144</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="C145" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="D145" s="11">
+        <v>70</v>
+      </c>
+      <c r="E145" s="11">
+        <v>72</v>
+      </c>
+      <c r="F145" s="10">
+        <v>80</v>
+      </c>
+      <c r="G145" s="72"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="72">
+        <v>145</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="C146" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="D146" s="11">
+        <v>90</v>
+      </c>
+      <c r="E146" s="11">
+        <v>74</v>
+      </c>
+      <c r="F146" s="10">
+        <v>90</v>
+      </c>
+      <c r="G146" s="72"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" s="72">
+        <v>146</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="C147" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="D147" s="76"/>
+      <c r="E147" s="11">
+        <v>68</v>
+      </c>
+      <c r="F147" s="77"/>
+      <c r="G147" s="72"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" s="72">
+        <v>147</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="C148" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="D148" s="76"/>
+      <c r="E148" s="11">
+        <v>75</v>
+      </c>
+      <c r="F148" s="77"/>
+      <c r="G148" s="72"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" s="72">
+        <v>148</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="C149" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="D149" s="76"/>
+      <c r="E149" s="11">
+        <v>70</v>
+      </c>
+      <c r="F149" s="77"/>
+      <c r="G149" s="72"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" s="72">
+        <v>149</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="C150" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="D150" s="11">
+        <v>70</v>
+      </c>
+      <c r="E150" s="11">
+        <v>70</v>
+      </c>
+      <c r="F150" s="10">
+        <v>80</v>
+      </c>
+      <c r="G150" s="72"/>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" s="72">
+        <v>150</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="C151" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="D151" s="76"/>
+      <c r="E151" s="11">
+        <v>72</v>
+      </c>
+      <c r="F151" s="77"/>
+      <c r="G151" s="72"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="72">
+        <v>151</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="C152" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="D152" s="11">
+        <v>80</v>
+      </c>
+      <c r="E152" s="11">
+        <v>66</v>
+      </c>
+      <c r="F152" s="10">
+        <v>70</v>
+      </c>
+      <c r="G152" s="72"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" s="72">
+        <v>152</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>683</v>
+      </c>
+      <c r="C153" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D153" s="11">
+        <v>70</v>
+      </c>
+      <c r="E153" s="11">
+        <v>72</v>
+      </c>
+      <c r="F153" s="10">
+        <v>80</v>
+      </c>
+      <c r="G153" s="72"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" s="72">
+        <v>153</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="C154" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="D154" s="11">
+        <v>70</v>
+      </c>
+      <c r="E154" s="11">
+        <v>69</v>
+      </c>
+      <c r="F154" s="10">
+        <v>80</v>
+      </c>
+      <c r="G154" s="72"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" s="72">
+        <v>154</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>684</v>
+      </c>
+      <c r="C155" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="D155" s="76"/>
+      <c r="E155" s="11">
+        <v>64</v>
+      </c>
+      <c r="F155" s="77"/>
+      <c r="G155" s="72"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" s="72">
+        <v>155</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>685</v>
+      </c>
+      <c r="C156" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="D156" s="76"/>
+      <c r="E156" s="11">
+        <v>75</v>
+      </c>
+      <c r="F156" s="77"/>
+      <c r="G156" s="72"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" s="72">
+        <v>156</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="C157" s="9" t="s">
         <v>682</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D30" s="10"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="44"/>
-    </row>
-    <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="43">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="44"/>
-    </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="43">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D32" s="10"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="44"/>
-    </row>
-    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="43">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="44"/>
-    </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="43">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D34" s="10"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="44"/>
-    </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="43">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D35" s="10"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="44"/>
-    </row>
-    <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="43">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" s="10"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="44"/>
-    </row>
-    <row r="37" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="43">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D37" s="10"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="44"/>
-    </row>
-    <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="43">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D38" s="10"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="44"/>
-    </row>
-    <row r="39" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="43">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D39" s="10"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="44"/>
-    </row>
-    <row r="40" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="43">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D40" s="10"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="44"/>
-    </row>
-    <row r="41" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="43">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D41" s="10"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="44"/>
-    </row>
-    <row r="42" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="43">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D42" s="10"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="44"/>
-    </row>
-    <row r="43" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="43">
-        <v>42</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D43" s="10"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="44"/>
-    </row>
-    <row r="44" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="43">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D44" s="10"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="44"/>
-    </row>
-    <row r="45" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="43">
-        <v>44</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D45" s="10"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="44"/>
-    </row>
-    <row r="46" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="43">
-        <v>45</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D46" s="10"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="44"/>
-    </row>
-    <row r="47" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="43">
-        <v>46</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D47" s="10"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="44"/>
-    </row>
-    <row r="48" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="43">
-        <v>47</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="D48" s="10"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="44"/>
-    </row>
-    <row r="49" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="43">
-        <v>48</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D49" s="10"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="44"/>
-    </row>
-    <row r="50" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="43">
-        <v>49</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="D50" s="10"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="44"/>
-    </row>
-    <row r="51" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="43">
-        <v>50</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="D51" s="10"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="44"/>
-    </row>
-    <row r="52" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="43">
-        <v>51</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="D52" s="10"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="44"/>
-    </row>
-    <row r="53" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="43">
-        <v>52</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D53" s="10"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="44"/>
-    </row>
-    <row r="54" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="43">
-        <v>53</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D54" s="10"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="44"/>
-    </row>
-    <row r="55" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="43">
-        <v>54</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D55" s="10"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="10"/>
-      <c r="G55" s="44"/>
-    </row>
-    <row r="56" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="43">
-        <v>55</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D56" s="10"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="44"/>
-    </row>
-    <row r="57" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="43">
-        <v>56</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D57" s="10"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="10"/>
-      <c r="G57" s="44"/>
-    </row>
-    <row r="58" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="43">
-        <v>57</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="D58" s="10"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="44"/>
-    </row>
-    <row r="59" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="43">
-        <v>58</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D59" s="10"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="44"/>
-    </row>
-    <row r="60" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="43">
-        <v>59</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="D60" s="10"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="10"/>
-      <c r="G60" s="44"/>
-    </row>
-    <row r="61" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="43">
-        <v>60</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="D61" s="10"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="10"/>
-      <c r="G61" s="44"/>
-    </row>
-    <row r="62" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="43">
-        <v>61</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="D62" s="10"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="10"/>
-      <c r="G62" s="44"/>
-    </row>
-    <row r="63" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="43">
-        <v>62</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D63" s="10"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="10"/>
-      <c r="G63" s="44"/>
-    </row>
-    <row r="64" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="43">
-        <v>63</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D64" s="10"/>
-      <c r="E64" s="11"/>
-      <c r="F64" s="10"/>
-      <c r="G64" s="44"/>
-    </row>
-    <row r="65" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="43">
-        <v>64</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D65" s="10"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="10"/>
-      <c r="G65" s="44"/>
-    </row>
-    <row r="66" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="43">
+      <c r="D157" s="76"/>
+      <c r="E157" s="11">
         <v>65</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D66" s="10"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="10"/>
-      <c r="G66" s="44"/>
-    </row>
-    <row r="67" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="43">
-        <v>66</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D67" s="10"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="10"/>
-      <c r="G67" s="44"/>
-    </row>
-    <row r="68" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="43">
-        <v>67</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D68" s="10"/>
-      <c r="E68" s="11"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="44"/>
-    </row>
-    <row r="69" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="43">
-        <v>68</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D69" s="10"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="10"/>
-      <c r="G69" s="44"/>
-    </row>
-    <row r="70" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="43">
-        <v>69</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D70" s="10"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="44"/>
-    </row>
-    <row r="71" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="43">
-        <v>70</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="D71" s="10"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="10"/>
-      <c r="G71" s="44"/>
-    </row>
-    <row r="72" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="43">
-        <v>71</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D72" s="10"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="10"/>
-      <c r="G72" s="44"/>
-    </row>
-    <row r="73" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="43">
-        <v>72</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="D73" s="10"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="10"/>
-      <c r="G73" s="44"/>
-    </row>
-    <row r="74" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="43">
-        <v>73</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="D74" s="10"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="44"/>
-    </row>
-    <row r="75" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="43">
-        <v>74</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="D75" s="10"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="10"/>
-      <c r="G75" s="44"/>
-    </row>
-    <row r="76" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="43">
-        <v>75</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="D76" s="10"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="44"/>
-    </row>
-    <row r="77" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="43">
-        <v>76</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D77" s="10"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="44"/>
-    </row>
-    <row r="78" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="43">
-        <v>77</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D78" s="10"/>
-      <c r="E78" s="11"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="44"/>
-    </row>
-    <row r="79" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="43">
-        <v>78</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>686</v>
-      </c>
-      <c r="D79" s="10"/>
-      <c r="E79" s="11"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="44"/>
-    </row>
-    <row r="80" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="43">
-        <v>79</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="D80" s="10"/>
-      <c r="E80" s="11"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="44"/>
-    </row>
-    <row r="81" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="43">
-        <v>80</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="D81" s="10"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="44"/>
-    </row>
-    <row r="82" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="43">
-        <v>81</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D82" s="10"/>
-      <c r="E82" s="11"/>
-      <c r="F82" s="10"/>
-      <c r="G82" s="44"/>
-    </row>
-    <row r="83" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="43">
-        <v>82</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="D83" s="10"/>
-      <c r="E83" s="11"/>
-      <c r="F83" s="10"/>
-      <c r="G83" s="44"/>
-    </row>
-    <row r="84" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="43">
-        <v>83</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D84" s="10"/>
-      <c r="E84" s="11"/>
-      <c r="F84" s="10"/>
-      <c r="G84" s="44"/>
-    </row>
-    <row r="85" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="43">
-        <v>84</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="D85" s="10"/>
-      <c r="E85" s="11"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="44"/>
-    </row>
-    <row r="86" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="43">
-        <v>85</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="D86" s="10"/>
-      <c r="E86" s="11"/>
-      <c r="F86" s="10"/>
-      <c r="G86" s="44"/>
-    </row>
-    <row r="87" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="43">
-        <v>86</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="D87" s="10"/>
-      <c r="E87" s="11"/>
-      <c r="F87" s="10"/>
-      <c r="G87" s="44"/>
-    </row>
-    <row r="88" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="43">
-        <v>87</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D88" s="10"/>
-      <c r="E88" s="11"/>
-      <c r="F88" s="10"/>
-      <c r="G88" s="44"/>
-    </row>
-    <row r="89" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="43">
-        <v>88</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="D89" s="10"/>
-      <c r="E89" s="11"/>
-      <c r="F89" s="10"/>
-      <c r="G89" s="44"/>
-    </row>
-    <row r="90" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="43">
-        <v>89</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="D90" s="10"/>
-      <c r="E90" s="11"/>
-      <c r="F90" s="10"/>
-      <c r="G90" s="44"/>
-    </row>
-    <row r="91" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="43">
-        <v>90</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="D91" s="10"/>
-      <c r="E91" s="11"/>
-      <c r="F91" s="10"/>
-      <c r="G91" s="44"/>
-    </row>
-    <row r="92" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="43">
-        <v>91</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="D92" s="10"/>
-      <c r="E92" s="11"/>
-      <c r="F92" s="10"/>
-      <c r="G92" s="44"/>
-    </row>
-    <row r="93" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="43">
-        <v>92</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="D93" s="10"/>
-      <c r="E93" s="11"/>
-      <c r="F93" s="10"/>
-      <c r="G93" s="44"/>
-    </row>
-    <row r="94" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="43">
-        <v>93</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="D94" s="10"/>
-      <c r="E94" s="11"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="44"/>
-    </row>
-    <row r="95" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="43">
-        <v>94</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="D95" s="10"/>
-      <c r="E95" s="11"/>
-      <c r="F95" s="10"/>
-      <c r="G95" s="44"/>
-    </row>
-    <row r="96" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="43">
-        <v>95</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="D96" s="10"/>
-      <c r="E96" s="11"/>
-      <c r="F96" s="10"/>
-      <c r="G96" s="44"/>
-    </row>
-    <row r="97" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="43">
-        <v>96</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="D97" s="10"/>
-      <c r="E97" s="11"/>
-      <c r="F97" s="10"/>
-      <c r="G97" s="44"/>
-    </row>
-    <row r="98" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="43">
-        <v>97</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="D98" s="10"/>
-      <c r="E98" s="11"/>
-      <c r="F98" s="10"/>
-      <c r="G98" s="44"/>
-    </row>
-    <row r="99" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="43">
-        <v>98</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="D99" s="10"/>
-      <c r="E99" s="11"/>
-      <c r="F99" s="10"/>
-      <c r="G99" s="44"/>
-    </row>
-    <row r="100" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="43">
-        <v>99</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="D100" s="10"/>
-      <c r="E100" s="11"/>
-      <c r="F100" s="10"/>
-      <c r="G100" s="44"/>
-    </row>
-    <row r="101" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="43">
-        <v>100</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="D101" s="10"/>
-      <c r="E101" s="11"/>
-      <c r="F101" s="10"/>
-      <c r="G101" s="44"/>
-    </row>
-    <row r="102" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="43">
-        <v>101</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="D102" s="10"/>
-      <c r="E102" s="11"/>
-      <c r="F102" s="10"/>
-      <c r="G102" s="44"/>
-    </row>
-    <row r="103" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="43">
-        <v>102</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="D103" s="10"/>
-      <c r="E103" s="11"/>
-      <c r="F103" s="10"/>
-      <c r="G103" s="44"/>
-    </row>
-    <row r="104" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="43">
-        <v>103</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="D104" s="10"/>
-      <c r="E104" s="11"/>
-      <c r="F104" s="10"/>
-      <c r="G104" s="44"/>
-    </row>
-    <row r="105" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="43">
-        <v>104</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="D105" s="10"/>
-      <c r="E105" s="11"/>
-      <c r="F105" s="10"/>
-      <c r="G105" s="44"/>
-    </row>
-    <row r="106" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="43">
-        <v>105</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="D106" s="10"/>
-      <c r="E106" s="11"/>
-      <c r="F106" s="10"/>
-      <c r="G106" s="44"/>
-    </row>
-    <row r="107" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="43">
-        <v>106</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="D107" s="10"/>
-      <c r="E107" s="11"/>
-      <c r="F107" s="10"/>
-      <c r="G107" s="44"/>
-    </row>
-    <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A108" s="43">
-        <v>107</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>689</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>690</v>
-      </c>
-      <c r="D108" s="10"/>
-      <c r="E108" s="11"/>
-      <c r="F108" s="10"/>
-      <c r="G108" s="44"/>
-    </row>
-    <row r="109" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="43">
-        <v>108</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D109" s="10"/>
-      <c r="E109" s="11"/>
-      <c r="F109" s="10"/>
-      <c r="G109" s="44"/>
-    </row>
-    <row r="110" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="43">
-        <v>109</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="D110" s="10"/>
-      <c r="E110" s="11"/>
-      <c r="F110" s="10"/>
-      <c r="G110" s="44"/>
-    </row>
-    <row r="111" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="43">
-        <v>110</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="D111" s="10"/>
-      <c r="E111" s="11"/>
-      <c r="F111" s="10"/>
-      <c r="G111" s="44"/>
-    </row>
-    <row r="112" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="43">
-        <v>111</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D112" s="10"/>
-      <c r="E112" s="11"/>
-      <c r="F112" s="10"/>
-      <c r="G112" s="44"/>
-    </row>
-    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="43">
-        <v>112</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C113" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="D113" s="10"/>
-      <c r="E113" s="11"/>
-      <c r="F113" s="10"/>
-      <c r="G113" s="44"/>
-    </row>
-    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="43">
-        <v>113</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C114" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="D114" s="10"/>
-      <c r="E114" s="11"/>
-      <c r="F114" s="10"/>
-      <c r="G114" s="44"/>
-    </row>
-    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="43">
-        <v>114</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="D115" s="10"/>
-      <c r="E115" s="11"/>
-      <c r="F115" s="10"/>
-      <c r="G115" s="44"/>
-    </row>
-    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="43">
-        <v>115</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C116" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="D116" s="10"/>
-      <c r="E116" s="11"/>
-      <c r="F116" s="10"/>
-      <c r="G116" s="44"/>
-    </row>
-    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="43">
-        <v>116</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C117" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="D117" s="10"/>
-      <c r="E117" s="11"/>
-      <c r="F117" s="10"/>
-      <c r="G117" s="44"/>
-    </row>
-    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="43">
-        <v>117</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="C118" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="D118" s="10"/>
-      <c r="E118" s="11"/>
-      <c r="F118" s="10"/>
-      <c r="G118" s="44"/>
-    </row>
-    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="43">
-        <v>118</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="C119" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D119" s="10"/>
-      <c r="E119" s="11"/>
-      <c r="F119" s="10"/>
-      <c r="G119" s="44"/>
-    </row>
-    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="43">
-        <v>119</v>
-      </c>
-      <c r="B120" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="C120" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="D120" s="10"/>
-      <c r="E120" s="11"/>
-      <c r="F120" s="10"/>
-      <c r="G120" s="44"/>
-    </row>
-    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="43">
-        <v>120</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="C121" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="D121" s="10"/>
-      <c r="E121" s="11"/>
-      <c r="F121" s="10"/>
-      <c r="G121" s="44"/>
-    </row>
-    <row r="122" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="46">
-        <v>121</v>
-      </c>
-      <c r="B122" s="67" t="s">
-        <v>268</v>
-      </c>
-      <c r="C122" s="48" t="s">
-        <v>269</v>
-      </c>
-      <c r="D122" s="51"/>
-      <c r="E122" s="50"/>
-      <c r="F122" s="51"/>
-      <c r="G122" s="68"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123">
-        <v>122</v>
-      </c>
-      <c r="B123" t="s">
-        <v>270</v>
-      </c>
-      <c r="C123" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124">
-        <v>123</v>
-      </c>
-      <c r="B124" t="s">
-        <v>272</v>
-      </c>
-      <c r="C124" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125">
-        <v>124</v>
-      </c>
-      <c r="B125" t="s">
-        <v>274</v>
-      </c>
-      <c r="C125" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126">
-        <v>125</v>
-      </c>
-      <c r="B126" t="s">
-        <v>276</v>
-      </c>
-      <c r="C126" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127">
-        <v>126</v>
-      </c>
-      <c r="B127" t="s">
-        <v>278</v>
-      </c>
-      <c r="C127" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128">
-        <v>127</v>
-      </c>
-      <c r="B128" t="s">
-        <v>280</v>
-      </c>
-      <c r="C128" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129">
-        <v>128</v>
-      </c>
-      <c r="B129" t="s">
-        <v>282</v>
-      </c>
-      <c r="C129" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130">
-        <v>129</v>
-      </c>
-      <c r="B130" t="s">
-        <v>284</v>
-      </c>
-      <c r="C130" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131">
-        <v>130</v>
-      </c>
-      <c r="B131" t="s">
-        <v>691</v>
-      </c>
-      <c r="C131" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132">
-        <v>131</v>
-      </c>
-      <c r="B132" t="s">
-        <v>287</v>
-      </c>
-      <c r="C132" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133">
-        <v>132</v>
-      </c>
-      <c r="B133" t="s">
-        <v>692</v>
-      </c>
-      <c r="C133" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134">
-        <v>133</v>
-      </c>
-      <c r="B134" t="s">
-        <v>693</v>
-      </c>
-      <c r="C134" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135">
-        <v>134</v>
-      </c>
-      <c r="B135" t="s">
-        <v>291</v>
-      </c>
-      <c r="C135" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136">
-        <v>135</v>
-      </c>
-      <c r="B136" t="s">
-        <v>293</v>
-      </c>
-      <c r="C136" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137">
-        <v>136</v>
-      </c>
-      <c r="B137" t="s">
-        <v>295</v>
-      </c>
-      <c r="C137" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138">
-        <v>137</v>
-      </c>
-      <c r="B138" t="s">
-        <v>694</v>
-      </c>
-      <c r="C138" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139">
-        <v>138</v>
-      </c>
-      <c r="B139" t="s">
-        <v>298</v>
-      </c>
-      <c r="C139" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140">
-        <v>139</v>
-      </c>
-      <c r="B140" t="s">
-        <v>300</v>
-      </c>
-      <c r="C140" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141">
-        <v>140</v>
-      </c>
-      <c r="B141" t="s">
-        <v>302</v>
-      </c>
-      <c r="C141" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142">
-        <v>141</v>
-      </c>
-      <c r="B142" t="s">
-        <v>304</v>
-      </c>
-      <c r="C142" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143">
-        <v>142</v>
-      </c>
-      <c r="B143" t="s">
-        <v>306</v>
-      </c>
-      <c r="C143" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144">
-        <v>143</v>
-      </c>
-      <c r="B144" t="s">
-        <v>695</v>
-      </c>
-      <c r="C144" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145">
-        <v>144</v>
-      </c>
-      <c r="B145" t="s">
-        <v>309</v>
-      </c>
-      <c r="C145" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146">
-        <v>145</v>
-      </c>
-      <c r="B146" t="s">
-        <v>311</v>
-      </c>
-      <c r="C146" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147">
-        <v>146</v>
-      </c>
-      <c r="B147" t="s">
-        <v>313</v>
-      </c>
-      <c r="C147" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148">
-        <v>147</v>
-      </c>
-      <c r="B148" t="s">
-        <v>696</v>
-      </c>
-      <c r="C148" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149">
-        <v>148</v>
-      </c>
-      <c r="B149" t="s">
-        <v>315</v>
-      </c>
-      <c r="C149" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150">
-        <v>149</v>
-      </c>
-      <c r="B150" t="s">
-        <v>317</v>
-      </c>
-      <c r="C150" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151">
-        <v>150</v>
-      </c>
-      <c r="B151" t="s">
-        <v>321</v>
-      </c>
-      <c r="C151" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152">
-        <v>151</v>
-      </c>
-      <c r="B152" t="s">
-        <v>323</v>
-      </c>
-      <c r="C152" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153">
-        <v>152</v>
-      </c>
-      <c r="B153" t="s">
-        <v>325</v>
-      </c>
-      <c r="C153" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154">
-        <v>153</v>
-      </c>
-      <c r="B154" t="s">
-        <v>327</v>
-      </c>
-      <c r="C154" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155">
-        <v>154</v>
-      </c>
-      <c r="B155" t="s">
-        <v>698</v>
-      </c>
-      <c r="C155" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156">
-        <v>155</v>
-      </c>
-      <c r="B156" t="s">
-        <v>329</v>
-      </c>
-      <c r="C156" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157">
-        <v>156</v>
-      </c>
-      <c r="B157" t="s">
-        <v>331</v>
-      </c>
-      <c r="C157" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158">
-        <v>157</v>
-      </c>
-      <c r="B158" t="s">
-        <v>335</v>
-      </c>
-      <c r="C158" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159">
-        <v>158</v>
-      </c>
-      <c r="B159" t="s">
-        <v>337</v>
-      </c>
-      <c r="C159" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160">
-        <v>159</v>
-      </c>
-      <c r="B160" t="s">
-        <v>339</v>
-      </c>
-      <c r="C160" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161">
-        <v>160</v>
-      </c>
-      <c r="B161" t="s">
-        <v>341</v>
-      </c>
-      <c r="C161" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162">
-        <v>161</v>
-      </c>
-      <c r="B162" t="s">
-        <v>343</v>
-      </c>
-      <c r="C162" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163">
-        <v>162</v>
-      </c>
-      <c r="B163" t="s">
-        <v>345</v>
-      </c>
-      <c r="C163" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164">
-        <v>163</v>
-      </c>
-      <c r="B164" t="s">
-        <v>700</v>
-      </c>
-      <c r="C164" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165">
-        <v>164</v>
-      </c>
-      <c r="B165" t="s">
-        <v>349</v>
-      </c>
-      <c r="C165" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166">
-        <v>165</v>
-      </c>
-      <c r="B166" t="s">
-        <v>351</v>
-      </c>
-      <c r="C166" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167">
-        <v>166</v>
-      </c>
-      <c r="B167" t="s">
-        <v>353</v>
-      </c>
-      <c r="C167" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168">
-        <v>167</v>
-      </c>
-      <c r="B168" t="s">
-        <v>355</v>
-      </c>
-      <c r="C168" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169">
-        <v>168</v>
-      </c>
-      <c r="B169" t="s">
-        <v>702</v>
-      </c>
-      <c r="C169" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170">
-        <v>169</v>
-      </c>
-      <c r="B170" t="s">
-        <v>358</v>
-      </c>
-      <c r="C170" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171">
-        <v>170</v>
-      </c>
-      <c r="B171" t="s">
-        <v>360</v>
-      </c>
-      <c r="C171" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172">
-        <v>171</v>
-      </c>
-      <c r="B172" t="s">
-        <v>376</v>
-      </c>
-      <c r="C172" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173">
-        <v>172</v>
-      </c>
-      <c r="B173" t="s">
-        <v>703</v>
-      </c>
-      <c r="C173" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174">
-        <v>173</v>
-      </c>
-      <c r="B174" t="s">
-        <v>406</v>
-      </c>
-      <c r="C174" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175">
-        <v>174</v>
-      </c>
-      <c r="B175" t="s">
-        <v>704</v>
-      </c>
-      <c r="C175" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176">
-        <v>175</v>
-      </c>
-      <c r="B176" t="s">
-        <v>412</v>
-      </c>
-      <c r="C176" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177">
-        <v>176</v>
-      </c>
-      <c r="B177" t="s">
-        <v>706</v>
-      </c>
-      <c r="C177" t="s">
-        <v>707</v>
-      </c>
+      <c r="F157" s="77"/>
+      <c r="G157" s="72"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20650,15 +21443,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
@@ -20667,6 +21451,15 @@
     <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20689,14 +21482,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -20711,4 +21496,12 @@
     <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Short Semester I (E24 Batch).xlsx
+++ b/Short Semester I (E24 Batch).xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maids.jfn\Documents\GitHub\MC3020_Attendance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoj-my.sharepoint.com/personal/mayooran_eng_jfn_ac_lk/Documents/Short_Semesters/app/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_74120E128ABF45D6F83E5D3831824F87064BC236" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{019BC034-A8CE-4E9F-B332-2F4BD54AC362}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MC9030" sheetId="2" r:id="rId1"/>
@@ -2100,7 +2101,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2242,18 +2243,12 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="19">
@@ -2521,7 +2516,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2712,7 +2707,7 @@
     <xf numFmtId="2" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2730,23 +2725,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 15" xfId="2"/>
-    <cellStyle name="Normal 2" xfId="3"/>
-    <cellStyle name="Normal 2 2" xfId="4"/>
-    <cellStyle name="Normal_Sheet1" xfId="1"/>
-    <cellStyle name="Normal_Sheet1_1" xfId="5"/>
+    <cellStyle name="Normal 15" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal_Sheet1" xfId="1" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal_Sheet1_1" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3023,7 +3009,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G210"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7446,7 +7432,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G178"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11208,7 +11194,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G123"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13794,7 +13780,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G198"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -17899,20 +17885,16 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" customWidth="1"/>
+    <col min="3" max="7" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="74" t="s">
         <v>0</v>
       </c>
@@ -17945,13 +17927,13 @@
       <c r="C2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="78">
+      <c r="D2" s="11">
         <v>0</v>
       </c>
       <c r="E2" s="11">
         <v>49</v>
       </c>
-      <c r="F2" s="77">
+      <c r="F2" s="10">
         <v>0</v>
       </c>
       <c r="G2" s="73"/>
@@ -18596,13 +18578,13 @@
       <c r="C33" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D33" s="78">
+      <c r="D33" s="11">
         <v>0</v>
       </c>
       <c r="E33" s="11">
         <v>72</v>
       </c>
-      <c r="F33" s="77">
+      <c r="F33" s="10">
         <v>0</v>
       </c>
       <c r="G33" s="73"/>
@@ -20476,7 +20458,7 @@
       </c>
       <c r="G122" s="73"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="72">
         <v>122</v>
       </c>
@@ -20497,7 +20479,7 @@
       </c>
       <c r="G123" s="72"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="72">
         <v>123</v>
       </c>
@@ -20518,7 +20500,7 @@
       </c>
       <c r="G124" s="72"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="72">
         <v>124</v>
       </c>
@@ -20539,7 +20521,7 @@
       </c>
       <c r="G125" s="72"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="72">
         <v>125</v>
       </c>
@@ -20560,7 +20542,7 @@
       </c>
       <c r="G126" s="72"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="72">
         <v>126</v>
       </c>
@@ -20581,7 +20563,7 @@
       </c>
       <c r="G127" s="72"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="72">
         <v>127</v>
       </c>
@@ -20602,7 +20584,7 @@
       </c>
       <c r="G128" s="72"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="72">
         <v>128</v>
       </c>
@@ -20623,7 +20605,7 @@
       </c>
       <c r="G129" s="72"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="72">
         <v>129</v>
       </c>
@@ -20644,7 +20626,7 @@
       </c>
       <c r="G130" s="72"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="72">
         <v>130</v>
       </c>
@@ -20665,7 +20647,7 @@
       </c>
       <c r="G131" s="72"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="72">
         <v>131</v>
       </c>
@@ -20681,10 +20663,10 @@
       <c r="E132" s="11">
         <v>70</v>
       </c>
-      <c r="F132" s="77"/>
+      <c r="F132" s="10"/>
       <c r="G132" s="72"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="72">
         <v>132</v>
       </c>
@@ -20705,7 +20687,7 @@
       </c>
       <c r="G133" s="72"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="72">
         <v>133</v>
       </c>
@@ -20726,7 +20708,7 @@
       </c>
       <c r="G134" s="72"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="72">
         <v>134</v>
       </c>
@@ -20747,7 +20729,7 @@
       </c>
       <c r="G135" s="72"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="72">
         <v>135</v>
       </c>
@@ -20768,7 +20750,7 @@
       </c>
       <c r="G136" s="72"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="72">
         <v>136</v>
       </c>
@@ -20789,7 +20771,7 @@
       </c>
       <c r="G137" s="72"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="72">
         <v>137</v>
       </c>
@@ -20810,7 +20792,7 @@
       </c>
       <c r="G138" s="72"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="72">
         <v>138</v>
       </c>
@@ -20831,7 +20813,7 @@
       </c>
       <c r="G139" s="72"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="72">
         <v>139</v>
       </c>
@@ -20852,7 +20834,7 @@
       </c>
       <c r="G140" s="72"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="72">
         <v>140</v>
       </c>
@@ -20873,7 +20855,7 @@
       </c>
       <c r="G141" s="72"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="72">
         <v>141</v>
       </c>
@@ -20894,7 +20876,7 @@
       </c>
       <c r="G142" s="72"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="72">
         <v>142</v>
       </c>
@@ -20915,7 +20897,7 @@
       </c>
       <c r="G143" s="72"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="72">
         <v>143</v>
       </c>
@@ -20936,7 +20918,7 @@
       </c>
       <c r="G144" s="72"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="72">
         <v>144</v>
       </c>
@@ -20957,7 +20939,7 @@
       </c>
       <c r="G145" s="72"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="72">
         <v>145</v>
       </c>
@@ -20978,7 +20960,7 @@
       </c>
       <c r="G146" s="72"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="72">
         <v>146</v>
       </c>
@@ -20988,14 +20970,14 @@
       <c r="C147" s="9" t="s">
         <v>577</v>
       </c>
-      <c r="D147" s="76"/>
+      <c r="D147" s="7"/>
       <c r="E147" s="11">
         <v>68</v>
       </c>
-      <c r="F147" s="77"/>
+      <c r="F147" s="10"/>
       <c r="G147" s="72"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="72">
         <v>147</v>
       </c>
@@ -21005,14 +20987,14 @@
       <c r="C148" s="9" t="s">
         <v>552</v>
       </c>
-      <c r="D148" s="76"/>
+      <c r="D148" s="7"/>
       <c r="E148" s="11">
         <v>75</v>
       </c>
-      <c r="F148" s="77"/>
+      <c r="F148" s="10"/>
       <c r="G148" s="72"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="72">
         <v>148</v>
       </c>
@@ -21022,14 +21004,14 @@
       <c r="C149" s="9" t="s">
         <v>553</v>
       </c>
-      <c r="D149" s="76"/>
+      <c r="D149" s="7"/>
       <c r="E149" s="11">
         <v>70</v>
       </c>
-      <c r="F149" s="77"/>
+      <c r="F149" s="10"/>
       <c r="G149" s="72"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="72">
         <v>149</v>
       </c>
@@ -21050,7 +21032,7 @@
       </c>
       <c r="G150" s="72"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="72">
         <v>150</v>
       </c>
@@ -21060,14 +21042,14 @@
       <c r="C151" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="D151" s="76"/>
+      <c r="D151" s="7"/>
       <c r="E151" s="11">
         <v>72</v>
       </c>
-      <c r="F151" s="77"/>
+      <c r="F151" s="10"/>
       <c r="G151" s="72"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="72">
         <v>151</v>
       </c>
@@ -21088,7 +21070,7 @@
       </c>
       <c r="G152" s="72"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="72">
         <v>152</v>
       </c>
@@ -21109,7 +21091,7 @@
       </c>
       <c r="G153" s="72"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="72">
         <v>153</v>
       </c>
@@ -21130,7 +21112,7 @@
       </c>
       <c r="G154" s="72"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="72">
         <v>154</v>
       </c>
@@ -21140,14 +21122,14 @@
       <c r="C155" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="D155" s="76"/>
+      <c r="D155" s="7"/>
       <c r="E155" s="11">
         <v>64</v>
       </c>
-      <c r="F155" s="77"/>
+      <c r="F155" s="10"/>
       <c r="G155" s="72"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="72">
         <v>155</v>
       </c>
@@ -21157,14 +21139,14 @@
       <c r="C156" s="9" t="s">
         <v>681</v>
       </c>
-      <c r="D156" s="76"/>
+      <c r="D156" s="7"/>
       <c r="E156" s="11">
         <v>75</v>
       </c>
-      <c r="F156" s="77"/>
+      <c r="F156" s="10"/>
       <c r="G156" s="72"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="72">
         <v>156</v>
       </c>
@@ -21174,11 +21156,11 @@
       <c r="C157" s="9" t="s">
         <v>682</v>
       </c>
-      <c r="D157" s="76"/>
+      <c r="D157" s="7"/>
       <c r="E157" s="11">
         <v>65</v>
       </c>
-      <c r="F157" s="77"/>
+      <c r="F157" s="10"/>
       <c r="G157" s="72"/>
     </row>
   </sheetData>
@@ -21188,6 +21170,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100455C4072EA7E0D46870C67AD0D3E62C3" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6d62d4992a7888825600c982e6c75641">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2835d969-06cc-46e6-b4cc-c525f784ce43" xmlns:ns3="03c84e3c-1549-479a-8619-e0d964aa7481" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9015832621b6abd41b87bce5adc31c29" ns2:_="" ns3:_="">
     <xsd:import namespace="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
@@ -21442,41 +21444,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46A244EB-A970-4F2B-8B12-6A24EFA3E1AE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
-    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -21499,9 +21470,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46A244EB-A970-4F2B-8B12-6A24EFA3E1AE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
+    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Short Semester I (E24 Batch).xlsx
+++ b/Short Semester I (E24 Batch).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoj-my.sharepoint.com/personal/mayooran_eng_jfn_ac_lk/Documents/Short_Semesters/app/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\theva\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_74120E128ABF45D6F83E5D3831824F87064BC236" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1CD33E7-FF5C-4D31-B2CB-2A2DDCA8619C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A544CC-DDCF-4F3B-AF8E-6BD8B44B1F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MC9030" sheetId="2" r:id="rId1"/>
@@ -10797,8 +10797,8 @@
       <c r="C2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="10">
-        <v>0</v>
+      <c r="D2" s="69">
+        <v>70</v>
       </c>
       <c r="E2" s="11">
         <v>47.5</v>
@@ -20806,6 +20806,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100455C4072EA7E0D46870C67AD0D3E62C3" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6d62d4992a7888825600c982e6c75641">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2835d969-06cc-46e6-b4cc-c525f784ce43" xmlns:ns3="03c84e3c-1549-479a-8619-e0d964aa7481" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9015832621b6abd41b87bce5adc31c29" ns2:_="" ns3:_="">
     <xsd:import namespace="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
@@ -21060,17 +21071,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -21081,6 +21081,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46A244EB-A970-4F2B-8B12-6A24EFA3E1AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21099,23 +21116,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
   <ds:schemaRefs>

--- a/Short Semester I (E24 Batch).xlsx
+++ b/Short Semester I (E24 Batch).xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\theva\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maids.jfn\Documents\GitHub\MC3020_Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A544CC-DDCF-4F3B-AF8E-6BD8B44B1F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="MC9030" sheetId="2" r:id="rId1"/>
@@ -1543,7 +1542,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2285,11 +2284,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 15" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal_Sheet1" xfId="1" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Normal_Sheet1_1" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal 15" xfId="2"/>
+    <cellStyle name="Normal 2" xfId="3"/>
+    <cellStyle name="Normal 2 2" xfId="4"/>
+    <cellStyle name="Normal_Sheet1" xfId="1"/>
+    <cellStyle name="Normal_Sheet1_1" xfId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2566,7 +2565,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G210"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6989,7 +6988,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G178"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10751,7 +10750,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G123"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13337,7 +13336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G198"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -17521,7 +17520,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20299,7 +20298,9 @@
       <c r="E132" s="11">
         <v>70</v>
       </c>
-      <c r="F132" s="10"/>
+      <c r="F132" s="10">
+        <v>70</v>
+      </c>
       <c r="G132" s="72"/>
     </row>
     <row r="133" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20806,14 +20807,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21072,27 +21071,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -21117,9 +21109,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Short Semester I (E24 Batch).xlsx
+++ b/Short Semester I (E24 Batch).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="MC9030" sheetId="2" r:id="rId1"/>
@@ -9814,7 +9814,7 @@
         <v>54</v>
       </c>
       <c r="F134" s="11">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G134" s="59"/>
     </row>
@@ -20807,12 +20807,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21071,20 +21073,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -21109,18 +21118,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>